--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_26_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_26_IN_Piura.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C10" s="31">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>76.91</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>20.75</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>2.35</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1917,11 +1917,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>46.9617</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>45.8595</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>97.65</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1967,11 +1967,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>1.1022</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>2.35</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2127,11 +2127,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>46.9733</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2250,6 +2250,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2485,6 +2486,7 @@
       <c r="F16" s="17" t="inlineStr"/>
       <c r="G16" s="17" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -2533,6 +2535,7 @@
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="96" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -3016,11 +3019,11 @@
       </c>
       <c r="B20" s="33">
         <f>SUM(B10:B19)</f>
-        <v/>
+        <v>552.18</v>
       </c>
       <c r="C20" s="23">
         <f>SUM(C10:C19)</f>
-        <v/>
+        <v>99.98</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -3030,19 +3033,19 @@
       <c r="E20" s="17" t="inlineStr"/>
       <c r="F20" s="17">
         <f>ROUND(AVERAGE(F10:F19),2)</f>
-        <v/>
+        <v>29.09</v>
       </c>
       <c r="G20" s="22">
         <f>ROUND(AVERAGE(G10:G19),4)</f>
-        <v/>
+        <v>0.6292</v>
       </c>
       <c r="H20" s="23">
         <f>ROUND(AVERAGE(H10:H19),2)</f>
-        <v/>
+        <v>93.19</v>
       </c>
       <c r="I20" s="23">
         <f>ROUND(AVERAGE(I10:I19),2)</f>
-        <v/>
+        <v>9.85</v>
       </c>
     </row>
     <row r="21"/>
